--- a/docs/razorpay-buildathon-idea-bank-FINAL-v5.xlsx
+++ b/docs/razorpay-buildathon-idea-bank-FINAL-v5.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Feasibility is 9.5 not because the idea is easy but because the repo exists and passes 371 tests today. On a one-day horizon that is the only variable that matters. It also absorbs the two ideas you wanted to merge: RazorGate's enforcement demo is gateway.py, RIWAAJ's cross-merchant shape is consortium.py — both as evaluation strategies over ONE predicate set, which is a stronger story than three separate products.
+          <t>Feasibility is 9.5 not because the idea is easy but because the repo exists and passes 421 tests today. On a one-day horizon that is the only variable that matters. It also absorbs the two ideas you wanted to merge: RazorGate's enforcement demo is gateway.py, RIWAAJ's cross-merchant shape is consortium.py — both as evaluation strategies over ONE predicate set, which is a stronger story than three separate products.
 The collision argument is the sharpest in the bank: Razorpay's guardrails blog describes certification (s8) and runtime validation (s4) as separate systems and never establishes that they agree. KASAUTI does not rebuild either. It ships the equivalence proof between them, which is the one artifact an outsider can construct and Razorpay has not published.</t>
         </is>
       </c>
@@ -1382,7 +1382,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RECOMMENDATION: ship KASAUTI. It exists, passes 371 tests, and now absorbs RazorGate (gateway.py) and RIWAAJ (consortium.py) as additional evaluation scopes over ONE predicate set.</t>
+          <t>RECOMMENDATION: ship KASAUTI. It exists, passes 421 tests, and now absorbs RazorGate (gateway.py) and RIWAAJ (consortium.py) as additional evaluation scopes over ONE predicate set.</t>
         </is>
       </c>
     </row>
